--- a/www/download/IND.gross_output.s.du.zdW13.xlsx
+++ b/www/download/IND.gross_output.s.du.zdW13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>130269.211989485</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>133253.651236831</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>132167.899191033</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>131940.534486347</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>144190.500859465</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>141972.689515986</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>134263.961447647</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>144006.069489255</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>161868.66372571</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>196371.312044168</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>213874.076525221</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>228576.112100939</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>271117.267418827</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>313398.957134197</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>298666.729383581</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64603.290778947</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67105.1632926629</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>63030.8343564675</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63768.119115707</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66697.4266849408</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71706.8937674205</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>70874.6593743138</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70424.7514027759</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78182.05560481</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89057.44281022</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93834.9199834883</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>106457.274977569</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>123974.076282579</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>143661.738968178</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>115042.441739898</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>82384.4496912924</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>77823.7357671771</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74522.8142495611</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74874.7296015944</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78540.2111286253</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>86823.8823786023</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83779.5355417079</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82864.2935625629</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95422.2401980469</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110716.105309894</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113502.675697585</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>128081.827910204</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>151971.246036199</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>198257.945460238</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>136929.996118079</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59341.2365609674</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62547.0184568001</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>57277.6507111347</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53920.9826277721</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52395.1014816449</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50680.1383089923</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47114.0419736099</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47503.6731856775</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52563.5069137119</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62056.1660977286</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67742.795777054</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75103.1652257705</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>87161.567497448</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95319.4413484451</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>87339.2714196931</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.223</t>
+          <t>1222816.43985586</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.218</t>
+          <t>1218127.11302743</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.211</t>
+          <t>1210545.67838298</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.168</t>
+          <t>1168086.8320629</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.245</t>
+          <t>1245291.46816276</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.288</t>
+          <t>1287991.02229227</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.213</t>
+          <t>1212956.31278629</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>1274856.74277269</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>1406200.2308101</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1628015.09371317</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.776</t>
+          <t>1776278.70717496</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>1842203.78589833</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.111</t>
+          <t>2111170.27381648</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.376</t>
+          <t>2375790.18555676</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.112</t>
+          <t>2112414.11234166</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>197544.616874803</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>203008.214783948</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>200634.774794897</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>200338.593413656</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>220244.082416461</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>246563.984828648</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>241483.514042474</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>239257.689959812</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>265874.06539364</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>318340.418304474</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>349129.903275616</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>373570.991545768</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>407138.522395139</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>456132.825477898</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>387923.554440293</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14.865</t>
+          <t>14865298.1147575</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15.433</t>
+          <t>15433223.7593341</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15.446</t>
+          <t>15446193.1074034</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15.317</t>
+          <t>15317223.7849036</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15799680.9388509</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>15.972</t>
+          <t>15971865.9055176</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15.875</t>
+          <t>15874802.1451434</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>16569900.5176997</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>18.904</t>
+          <t>18904136.7938255</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>21.315</t>
+          <t>21315370.6845353</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>24.081</t>
+          <t>24080584.8257917</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>27.722</t>
+          <t>27721982.6120519</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>32.802</t>
+          <t>32801695.2495302</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>37.386</t>
+          <t>37385720.9536703</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>35.373</t>
+          <t>35372585.2605871</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4495.81167509041</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4992.3214954997</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4421.93124023906</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4426.17806849223</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4939.16906046708</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4991.1651471663</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5391.05775674997</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5703.48201998843</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6315.69503136983</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6606.45610093257</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6534.13534702762</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7020.85158173797</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7647.04452397014</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11791.1549239647</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7740.6773805208</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102508.652875926</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>104215.494456868</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>104320.33166935</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>101656.348709783</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>102010.07501376</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>100342.621608906</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>98541.6602548556</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>101572.659998042</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108734.79491259</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>123301.521210254</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>132667.189255719</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>149404.498487563</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>175339.153751341</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>201352.35574172</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>157008.077930365</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>623744.113875304</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>579750.662264261</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>551257.247681793</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>565619.760625302</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>589592.142784104</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>633442.442632405</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.586</t>
+          <t>585639.66675259</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>572401.434571543</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>656414.985927404</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.758</t>
+          <t>758011.616126745</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>802118.426921584</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>888484.643945606</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.054</t>
+          <t>1053817.87793964</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1.168</t>
+          <t>1168403.11005509</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>913142.1513752</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51959.0898816006</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51906.4420642031</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49455.8152556116</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49432.7481515708</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48288.2881585151</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50113.3389196909</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50130.5968256552</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50549.716431079</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>57105.1774663357</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63773.5541974271</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66747.740441826</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71910.6824272679</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82747.1213156</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>93222.2396608565</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74267.883423525</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>249508.315954828</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>250856.946835815</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>240151.943182092</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>253694.983923526</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>283912.933396425</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>312072.203775726</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>307359.63973891</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>330325.493937329</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>363108.014524305</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>418168.989061258</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>467499.251075292</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>511442.431355131</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>588641.518692487</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.654</t>
+          <t>654126.619427965</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>485057.6488747</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11423.7494949208</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11255.2059275952</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11661.8588670214</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11731.6284841485</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11155.3269618698</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12042.4869872937</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12503.2789998662</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13496.146913124</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15308.1697439735</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17993.576121159</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17944.0366202113</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19261.2871992314</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20177.8992548979</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21266.1963223691</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15921.9186282511</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46437.1033796343</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47636.4989936808</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47339.834252101</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49858.4588197418</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55528.6402048176</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56718.0854414058</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51883.206253565</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52651.5639127789</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58532.6035517114</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66600.3371127737</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>73979.6182957238</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>80264.9961199503</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>92416.4166722631</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>106447.674004835</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74083.779353586</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>354065.396415013</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>347157.231102735</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>319182.639587398</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>326450.85865964</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>359053.53231127</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>379584.785701239</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>366241.358901489</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>362405.19548598</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>403976.960700744</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>456433.172883241</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>494023.411405992</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>526066.08077319</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>608364.030956948</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>693815.118137315</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>570735.775287272</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>382549.365458926</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>390754.185297083</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>374495.167603472</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>367033.151786774</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>377273.738184902</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>381622.592161219</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>366155.085679747</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>366431.983239249</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>399136.725568483</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>459660.396293842</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>503506.63929653</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.535</t>
+          <t>535382.118418111</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>600964.059333203</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>630846.78857558</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>530560.002709647</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76505.3217206359</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78738.9936837947</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72248.5870760078</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>70973.7872210877</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74221.6586948004</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80883.4742129395</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74912.8272356716</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76235.2784419317</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81098.9997388996</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>86923.8104368021</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>93133.6371492839</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>104095.785995634</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>117138.883231055</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>129021.135477121</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109467.696062519</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>77650.266606078</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79044.1484052147</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76252.1402919973</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77098.2212114193</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>84855.5791835794</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86365.1228729573</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81772.0510441767</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83222.9248826329</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89017.2407172786</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93514.3178941678</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>98529.3991062648</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>104116.899073387</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>119935.2161489</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>127461.062881964</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>106886.463767964</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.178</t>
+          <t>1177584.03878854</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1229619.34035444</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.189</t>
+          <t>1189294.64480556</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1110040.28287929</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1304636.23918137</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>1398135.69847021</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1390047.64308516</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.507</t>
+          <t>1507371.37407756</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.675</t>
+          <t>1674850.94839292</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.822</t>
+          <t>1821718.12979038</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.737</t>
+          <t>1736742.57772274</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.744</t>
+          <t>1743716.75011657</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2.051</t>
+          <t>2051296.46096251</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.294</t>
+          <t>2294168.23440833</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2.248</t>
+          <t>2247571.60440805</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9.566</t>
+          <t>9566403.87353724</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9779923.40930081</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>9.924</t>
+          <t>9924277.92636817</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>9.807</t>
+          <t>9807090.27017453</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>9.868</t>
+          <t>9867756.16194268</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>10.463</t>
+          <t>10463273.4748225</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10.474</t>
+          <t>10474174.6687811</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>10.568</t>
+          <t>10568238.5791672</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>12.229</t>
+          <t>12229179.1687422</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>13.813</t>
+          <t>13813464.0794693</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>15.123</t>
+          <t>15122983.4280252</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>15.986</t>
+          <t>15986044.942519</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>17.483</t>
+          <t>17482956.7141077</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>19.026</t>
+          <t>19025907.531346</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>18.033</t>
+          <t>18033146.6436471</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33245.5830161084</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34373.6523553441</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33575.1528421277</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33146.9661686571</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37920.5080860644</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41438.7053559384</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41486.0291847065</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40239.2961756979</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45867.2279162961</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55284.8022574224</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62309.6407878308</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68076.4572074201</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79311.264401958</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81313.2622116285</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66820.4605242324</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>429746.108216222</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>428218.011037852</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>405973.900402304</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.414</t>
+          <t>413709.868128396</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>432931.034005299</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>466521.904464321</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>451042.879934504</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>454945.077479949</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>505837.130075479</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>579840.085209978</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.616</t>
+          <t>616290.781685597</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.693</t>
+          <t>693200.064048817</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.785</t>
+          <t>785460.873922504</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>869613.810244264</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.661</t>
+          <t>661238.07688035</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1488569.712561</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.431</t>
+          <t>1430954.05750752</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1365631.44391473</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1218932.84012892</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>1273392.57343461</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1350189.36426481</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>1251433.25225476</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.214</t>
+          <t>1214032.94995828</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.347</t>
+          <t>1347049.73693867</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1550182.42845738</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1.654</t>
+          <t>1653548.33128983</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1.785</t>
+          <t>1785059.47733638</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1.983</t>
+          <t>1983138.92799657</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.243</t>
+          <t>2243270.46952153</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.717</t>
+          <t>1717167.77942718</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>624957.8226798</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.628</t>
+          <t>627800.052378387</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>610640.101870265</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>520417.624163814</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>580808.948571366</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>636326.205402011</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>600926.47574459</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>624895.837186829</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.693</t>
+          <t>692594.901138152</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.825</t>
+          <t>824810.186284925</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.878</t>
+          <t>877543.593997142</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>960336.013673242</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1.084</t>
+          <t>1083991.50430806</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1.237</t>
+          <t>1236686.25809426</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.053</t>
+          <t>1052562.64084213</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25643.5189113818</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25427.5151098798</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22807.6795942686</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24159.1479033289</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23470.5786546861</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24524.4502077631</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23196.2148573609</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23982.7699205988</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26708.917553651</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28164.6456689691</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31591.727494781</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32572.2347538057</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37433.5132412234</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43097.9266279286</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34136.1623034002</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3427.86038592202</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3082.7937921956</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2867.93228762258</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3066.05670816302</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2939.13785122425</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3352.01630717763</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3117.25390380474</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3261.38636270753</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3983.21911553444</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4880.59181942136</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5276.8388218771</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5716.74267180123</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6419.45209035859</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7415.81127218961</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6356.16763050143</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12062.3035333225</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11916.4001381624</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12186.8871189222</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12181.2382947907</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11739.5334684233</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10785.9409127848</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10457.0448431147</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10698.1284430194</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12506.3067789173</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14868.4466203656</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16431.4586373585</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18420.2508043262</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22880.7264106356</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22450.3047511349</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14766.2511247878</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>545282.072257028</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.576</t>
+          <t>575737.2202094</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>565574.748849276</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.587</t>
+          <t>586869.875441848</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>634371.893812897</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>667084.163997013</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>658730.157106811</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>670315.433924792</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>737372.615050893</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.853</t>
+          <t>852690.187759761</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>919028.99537833</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.964</t>
+          <t>963613.638524019</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.077</t>
+          <t>1076996.00638923</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.261</t>
+          <t>1261151.32644905</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>1132786.03790778</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2341.53002603478</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2347.0411352479</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2043.68757112711</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2150.20405919576</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2502.3680905213</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2853.98578606294</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2301.49996341846</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2478.07760353164</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2676.40912685284</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2800.19089265576</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2793.26244784637</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3225.65375631033</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3657.84901905573</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4152.92457836375</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3354.01957156543</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>158684.514485839</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>163808.747090459</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149641.857519772</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>165269.139876151</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>182397.063447998</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>185047.260170433</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>187241.265487066</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>162100.225922104</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>211656.050698485</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>234146.853353858</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>260978.306859287</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>273864.626027861</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>323136.83738468</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>393464.899605168</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>320367.100921705</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>308014.785517216</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>315837.359656856</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>307729.039060916</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>303930.439637123</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>300733.56985711</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>310237.640949472</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>260003.669926663</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>252189.753882966</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>267577.703350629</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>302389.200648387</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>331186.722175353</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>360948.761681635</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>431618.702765205</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>500097.753890102</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>421820.444623455</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97476.2869029017</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97378.1758656389</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>91940.5299870144</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95458.1402283431</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>98716.9242309583</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>106828.178840154</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>103739.173386991</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103014.209624296</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108657.503619824</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>121406.173670384</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>124990.663742031</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>130138.965416634</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>150318.704481816</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>167792.283389033</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>135116.01382157</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>216506.600398774</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>229498.623676676</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>205839.462784996</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>187020.359691098</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>244278.454235964</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>240811.763094979</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>227559.406890578</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>198366.541613203</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>209471.470926225</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>221620.203643991</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>234560.180126535</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>244928.956666115</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>279317.453628889</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>307479.510827423</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>271149.182478735</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.472</t>
+          <t>1472370.96217458</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1475043.69423908</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.379</t>
+          <t>1379228.80243951</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.274</t>
+          <t>1274426.26178917</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.282</t>
+          <t>1281650.02114786</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.338</t>
+          <t>1337597.01185017</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1318208.90929378</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1311471.74255602</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1410369.04564453</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>1528227.51732939</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.633</t>
+          <t>1633334.2986874</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1670265.36613553</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.956</t>
+          <t>1955901.27481274</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2.157</t>
+          <t>2157100.16978171</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1970033.44741163</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42174.048178861</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42353.2999541374</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39332.4125934725</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37610.565429189</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37376.1090679135</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37878.2257371084</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36741.1754456945</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36072.1083750414</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39409.1364944163</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44306.3978372504</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48899.7732866527</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54875.0585822795</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68390.0459555015</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77186.0977859862</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66836.8470455715</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19574.3532241692</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19200.0646337458</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17893.1499958675</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17820.8252575326</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18562.795397257</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19726.9977181084</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19221.944510169</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19418.2187729392</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21884.217103768</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23844.7371631567</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25219.028245417</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27266.6690638328</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32065.6778871168</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37854.8647111493</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30514.082361802</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72793.5403970605</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>70556.6858363801</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68113.0325542502</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70213.9177765865</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74082.7664092368</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80847.8731006336</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74709.2653287235</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74409.3552015416</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82727.4404499184</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>94357.0334810677</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>103633.843914669</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>109948.645979436</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>130291.450020493</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>143068.466501401</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>111980.547346468</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.425</t>
+          <t>425248.287425238</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>439364.348763993</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>445291.427967462</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>431882.372835017</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>456969.589994567</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>461467.915007554</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>434875.259483217</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>448311.965225796</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>495689.913632565</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>566585.533698147</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>602427.173443696</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>610291.789624993</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>675659.923929883</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.789</t>
+          <t>789463.655529019</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>644730.213939482</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>269105.974791827</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>264566.747536377</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>255955.540838914</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>245138.039536187</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>252623.918112354</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>275351.524460906</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>239212.50260029</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>256866.726194654</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>290727.419122506</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>358503.38859589</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>371063.100316708</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>398378.726085812</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>448376.776849995</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>498801.010184129</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>378523.316329816</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.918</t>
+          <t>1917855.44737794</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.947</t>
+          <t>1946932.70581806</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.971</t>
+          <t>1970724.34142294</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1989879.39034266</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2140022.52188965</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2.304</t>
+          <t>2303786.84099641</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2.119</t>
+          <t>2118840.92409373</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2.078</t>
+          <t>2077502.57829095</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2269505.05501947</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2.657</t>
+          <t>2657382.85741537</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2.935</t>
+          <t>2935030.05416534</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3150381.03070587</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>3.423</t>
+          <t>3423314.44600271</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3739813.37135777</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2.877</t>
+          <t>2877022.56591401</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>17670134.7640659</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>18.201</t>
+          <t>18201052.3175418</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>18.497</t>
+          <t>18496826.3407095</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>18.622</t>
+          <t>18622144.9045018</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>19.449</t>
+          <t>19448642.3096824</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>20.438</t>
+          <t>20437511.9239148</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>20609654.757445</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21759786.6316304</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24319993.405608</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>27.651</t>
+          <t>27651335.632265</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>30.358</t>
+          <t>30358138.7082923</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>33.164</t>
+          <t>33164418.43728</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>37.444</t>
+          <t>37444154.8822197</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>42.082</t>
+          <t>42082096.3532651</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>40.404</t>
+          <t>40404332.280805</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>55.182</t>
+          <t>55182308.5366997</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>56.556</t>
+          <t>56556389.0503581</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>56.599</t>
+          <t>56598550.2992956</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>56.061</t>
+          <t>56060688.4328248</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>58.306</t>
+          <t>58306395.8341117</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>60.817</t>
+          <t>60817361.9019018</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>60.203</t>
+          <t>60202725.9733039</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>62.264</t>
+          <t>62263778.5854962</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>70.209</t>
+          <t>70209291.8668545</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>79.624</t>
+          <t>79623724.2735859</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>87.526</t>
+          <t>87525633.878685</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>95.929</t>
+          <t>95929115.303749</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>109.398</t>
+          <t>109397506.893586</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>122.789</t>
+          <t>122789481.799157</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>114.158</t>
+          <t>114158105.32809</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gross_output.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
